--- a/mode_docx_gen/part/lvrbvtr2/RVTR1.xlsx
+++ b/mode_docx_gen/part/lvrbvtr2/RVTR1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.11.240\Company\Ivanovo\Документация ЮНИТ М300\Разработка\Схемы ФБ ЮНИТ-М3\Трансформатор\ИЭУ Т 35 кВ Россети\01. Разработка ФБ\58. КЦН НН2 Т2\_xlsx\funcs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\www_obj\mode_docx_gen\part\lvrbvtr2\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C41721-F5EE-4A6D-BB87-61B84BC5B54E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26820" windowHeight="9060"/>
+    <workbookView xWindow="38280" yWindow="2325" windowWidth="15600" windowHeight="18720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Signals" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="109">
   <si>
     <t>Категория (group)</t>
   </si>
@@ -229,88 +230,109 @@
     <t>U2ср</t>
   </si>
   <si>
+    <t>U2&gt;</t>
+  </si>
+  <si>
+    <t>StrValU</t>
+  </si>
+  <si>
+    <t>StrValU2</t>
+  </si>
+  <si>
+    <t>Выдержка времени срабатывания</t>
+  </si>
+  <si>
+    <t>Tср</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>INT32</t>
+  </si>
+  <si>
+    <t>мс</t>
+  </si>
+  <si>
+    <t>ING</t>
+  </si>
+  <si>
+    <t>LVRVTR</t>
+  </si>
+  <si>
+    <t>КЦН</t>
+  </si>
+  <si>
+    <t>Пуск органа минимального напряжения</t>
+  </si>
+  <si>
+    <t>Пуск по Uлин</t>
+  </si>
+  <si>
+    <t>Пуск органа максимального напряжения ОП</t>
+  </si>
+  <si>
+    <t>Пуск по U2</t>
+  </si>
+  <si>
+    <t>Неисправность цепей напряжения</t>
+  </si>
+  <si>
+    <t>Неиспр. ЦН</t>
+  </si>
+  <si>
+    <t>Ввод функции в работу</t>
+  </si>
+  <si>
+    <t>Ввод_функции</t>
+  </si>
+  <si>
+    <t>0 - Не предусмотрено, 1 - Предусмотрено</t>
+  </si>
+  <si>
+    <t>SPS</t>
+  </si>
+  <si>
+    <t>RVTR1</t>
+  </si>
+  <si>
+    <t>StrUpp</t>
+  </si>
+  <si>
+    <t>StrU2</t>
+  </si>
+  <si>
+    <t>Alm</t>
+  </si>
+  <si>
+    <t>AlmDlTmms</t>
+  </si>
+  <si>
+    <t>В</t>
+  </si>
+  <si>
     <t>U&lt;</t>
   </si>
   <si>
-    <t>U2&gt;</t>
-  </si>
-  <si>
-    <t>StrValU</t>
-  </si>
-  <si>
-    <t>StrValU2</t>
-  </si>
-  <si>
-    <t>Выдержка времени срабатывания</t>
-  </si>
-  <si>
-    <t>Tср</t>
-  </si>
-  <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>INT32</t>
-  </si>
-  <si>
-    <t>мс</t>
-  </si>
-  <si>
-    <t>ING</t>
-  </si>
-  <si>
-    <t>LVRVTR</t>
-  </si>
-  <si>
-    <t>Пуск органа минимального напряжения</t>
-  </si>
-  <si>
-    <t>Пуск по Uлин</t>
-  </si>
-  <si>
-    <t>Пуск органа максимального напряжения ОП</t>
-  </si>
-  <si>
-    <t>Пуск по U2</t>
-  </si>
-  <si>
-    <t>Неисправность цепей напряжения</t>
-  </si>
-  <si>
-    <t>Неиспр. ЦН</t>
-  </si>
-  <si>
-    <t>Ввод функции в работу</t>
-  </si>
-  <si>
-    <t>Ввод_функции</t>
-  </si>
-  <si>
-    <t>0 - Не предусмотрено, 1 - Предусмотрено</t>
-  </si>
-  <si>
-    <t>SPS</t>
-  </si>
-  <si>
-    <t>RVTR1</t>
-  </si>
-  <si>
-    <t>StrUpp</t>
-  </si>
-  <si>
-    <t>StrU2</t>
-  </si>
-  <si>
-    <t>Alm</t>
-  </si>
-  <si>
-    <t>AlmDlTmms</t>
-  </si>
-  <si>
-    <t>В</t>
-  </si>
-  <si>
-    <t>КЦН</t>
+    <t>DescriptionFunc</t>
+  </si>
+  <si>
+    <t>WeightFunc</t>
+  </si>
+  <si>
+    <t>Сигнализация неисправности цепей напряжения</t>
+  </si>
+  <si>
+    <t>Режим пуска</t>
+  </si>
+  <si>
+    <t>Реж_пуска</t>
+  </si>
+  <si>
+    <t>SGF2</t>
+  </si>
+  <si>
+    <t>0 - Внутренний, 1 - Внешний</t>
   </si>
   <si>
     <t>КЦН НН2</t>
@@ -319,31 +341,19 @@
     <t>LVRBVTR2</t>
   </si>
   <si>
-    <t>DescriptionFunc</t>
-  </si>
-  <si>
-    <t>Сигнализация неисправности цепей напряжения</t>
-  </si>
-  <si>
-    <t>WeightFunc</t>
-  </si>
-  <si>
-    <t>Режим пуска</t>
-  </si>
-  <si>
-    <t>Реж_пуска</t>
-  </si>
-  <si>
-    <t>SGF2</t>
-  </si>
-  <si>
-    <t>0 - Внутренний, 1 - Внешний</t>
+    <t>alias</t>
+  </si>
+  <si>
+    <t>Umin</t>
+  </si>
+  <si>
+    <t>U2max</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -380,7 +390,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -416,11 +426,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -428,9 +449,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -737,14 +761,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AD14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AE14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="3" width="43.85546875" customWidth="1"/>
-    <col min="4" max="4" width="35.140625" customWidth="1"/>
+    <col min="4" max="4" width="20.42578125" customWidth="1"/>
     <col min="5" max="5" width="25.28515625" customWidth="1"/>
     <col min="6" max="6" width="49.42578125" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" customWidth="1"/>
@@ -752,7 +776,7 @@
     <col min="28" max="28" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -843,13 +867,16 @@
       <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="AE1" s="6" t="s">
+        <v>106</v>
+      </c>
     </row>
-    <row r="2" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>34</v>
@@ -882,7 +909,7 @@
         <v>31</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>37</v>
@@ -936,12 +963,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>44</v>
@@ -974,7 +1001,7 @@
         <v>31</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>37</v>
@@ -1028,12 +1055,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>55</v>
@@ -1066,7 +1093,7 @@
         <v>31</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N4" s="3" t="s">
         <v>31</v>
@@ -1120,12 +1147,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>57</v>
@@ -1158,7 +1185,7 @@
         <v>31</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N5" s="3" t="s">
         <v>31</v>
@@ -1212,12 +1239,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>80</v>
@@ -1250,7 +1277,7 @@
         <v>31</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>89</v>
@@ -1304,12 +1331,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>82</v>
@@ -1342,7 +1369,7 @@
         <v>31</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N7" s="3" t="s">
         <v>89</v>
@@ -1396,12 +1423,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>53</v>
@@ -1434,7 +1461,7 @@
         <v>31</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>31</v>
@@ -1488,12 +1515,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>84</v>
@@ -1526,7 +1553,7 @@
         <v>31</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>89</v>
@@ -1580,12 +1607,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>86</v>
@@ -1618,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>31</v>
@@ -1672,24 +1699,24 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:30" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>103</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>105</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>32</v>
@@ -1710,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N11" s="5" t="s">
         <v>31</v>
@@ -1764,12 +1791,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>65</v>
@@ -1778,7 +1805,7 @@
         <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>31</v>
@@ -1802,7 +1829,7 @@
         <v>6</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>49</v>
@@ -1847,7 +1874,7 @@
         <v>90</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AC12" s="3" t="s">
         <v>31</v>
@@ -1855,13 +1882,16 @@
       <c r="AD12" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="AE12" s="3" t="s">
+        <v>107</v>
+      </c>
     </row>
-    <row r="13" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>66</v>
@@ -1870,7 +1900,7 @@
         <v>68</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>31</v>
@@ -1894,7 +1924,7 @@
         <v>6</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>49</v>
@@ -1939,7 +1969,7 @@
         <v>90</v>
       </c>
       <c r="AB13" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AC13" s="3" t="s">
         <v>31</v>
@@ -1947,31 +1977,34 @@
       <c r="AD13" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="AE13" s="3" t="s">
+        <v>108</v>
+      </c>
     </row>
-    <row r="14" spans="1:30" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
@@ -1986,16 +2019,16 @@
         <v>500</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>52</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>31</v>
@@ -2039,9 +2072,12 @@
       <c r="AD14" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="AE14" s="3" t="s">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
-  <sortState ref="A2:AD24">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD24">
     <sortCondition ref="A1"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2050,7 +2086,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2070,7 +2106,7 @@
         <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2078,7 +2114,7 @@
         <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2088,15 +2124,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" t="s">
         <v>99</v>
-      </c>
-      <c r="B5" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B6">
         <v>10</v>
